--- a/1.BlindTest/XII/BTXIIA/BTXIIA.xlsx
+++ b/1.BlindTest/XII/BTXIIA/BTXIIA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lspri\Dropbox (UCL)\Temporary Folder for Github\1.BlindTest\XII\BTXIIA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6CC77A6C-9B95-4D8B-B6F7-BADE35FF2F4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FAB3EC08-84BA-4883-B666-3D6D017B0CDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{BFC6B304-3B6A-4AA4-A303-A54B62CB367C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5AF2481D-818E-4935-B4C7-64AEEEBFF619}"/>
   </bookViews>
   <sheets>
     <sheet name="BTXIIA_forxls" sheetId="1" r:id="rId1"/>
@@ -20,9 +20,21 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="830" uniqueCount="446">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="834" uniqueCount="450">
   <si>
     <t>Filename</t>
+  </si>
+  <si>
+    <t>Density 1 /gcm-3</t>
+  </si>
+  <si>
+    <t>Lattice Energy 1 /kJmol-1</t>
+  </si>
+  <si>
+    <t>Unit Cell Free Energy 1 /kJmol-1</t>
+  </si>
+  <si>
+    <t>Packing Coefficient 1</t>
   </si>
   <si>
     <t>Space Group</t>
@@ -2217,7 +2229,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2261F6F1-5E43-492A-B292-723A922E791A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FE7FBD5-69CC-46CB-A68C-CBB1DB184A98}">
   <dimension ref="A1:G414"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -2225,28 +2237,28 @@
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1">
-        <v>1.0498099999999999</v>
-      </c>
-      <c r="C1">
-        <v>-33.762999999999998</v>
-      </c>
-      <c r="D1">
-        <v>-38.701599999999999</v>
-      </c>
-      <c r="E1">
-        <v>0.67389699999999997</v>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G1" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B2">
         <v>1.0638529999999999</v>
@@ -2261,15 +2273,15 @@
         <v>0.67483800000000005</v>
       </c>
       <c r="F2" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B3">
         <v>1.096646</v>
@@ -2284,12 +2296,12 @@
         <v>0.69509699999999996</v>
       </c>
       <c r="F3" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B4">
         <v>1.0876410000000001</v>
@@ -2304,12 +2316,12 @@
         <v>0.688967</v>
       </c>
       <c r="F4" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B5">
         <v>1.0716699999999999</v>
@@ -2324,12 +2336,12 @@
         <v>0.68478000000000006</v>
       </c>
       <c r="F5" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B6">
         <v>1.0591759999999999</v>
@@ -2344,12 +2356,12 @@
         <v>0.66999699999999995</v>
       </c>
       <c r="F6" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B7">
         <v>1.0722210000000001</v>
@@ -2364,12 +2376,12 @@
         <v>0.678728</v>
       </c>
       <c r="F7" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B8">
         <v>1.0557970000000001</v>
@@ -2384,12 +2396,12 @@
         <v>0.67216600000000004</v>
       </c>
       <c r="F8" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B9">
         <v>1.0795779999999999</v>
@@ -2404,12 +2416,12 @@
         <v>0.68095399999999995</v>
       </c>
       <c r="F9" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B10">
         <v>1.0526310000000001</v>
@@ -2424,12 +2436,12 @@
         <v>0.67208199999999996</v>
       </c>
       <c r="F10" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B11">
         <v>1.0825180000000001</v>
@@ -2444,12 +2456,12 @@
         <v>0.68842000000000003</v>
       </c>
       <c r="F11" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B12">
         <v>1.0730040000000001</v>
@@ -2464,12 +2476,12 @@
         <v>0.67989999999999995</v>
       </c>
       <c r="F12" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B13">
         <v>1.0864259999999999</v>
@@ -2484,12 +2496,12 @@
         <v>0.68460600000000005</v>
       </c>
       <c r="F13" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="B14">
         <v>1.075024</v>
@@ -2504,12 +2516,12 @@
         <v>0.68069800000000003</v>
       </c>
       <c r="F14" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B15">
         <v>1.06246</v>
@@ -2524,12 +2536,12 @@
         <v>0.66699799999999998</v>
       </c>
       <c r="F15" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="B16">
         <v>1.0641350000000001</v>
@@ -2544,12 +2556,12 @@
         <v>0.67582600000000004</v>
       </c>
       <c r="F16" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="B17">
         <v>1.0806709999999999</v>
@@ -2564,12 +2576,12 @@
         <v>0.68821200000000005</v>
       </c>
       <c r="F17" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="B18">
         <v>1.066173</v>
@@ -2584,12 +2596,12 @@
         <v>0.68195899999999998</v>
       </c>
       <c r="F18" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B19">
         <v>1.0659130000000001</v>
@@ -2604,12 +2616,12 @@
         <v>0.67290899999999998</v>
       </c>
       <c r="F19" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B20">
         <v>1.07196</v>
@@ -2624,12 +2636,12 @@
         <v>0.675238</v>
       </c>
       <c r="F20" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B21">
         <v>1.061288</v>
@@ -2644,12 +2656,12 @@
         <v>0.671157</v>
       </c>
       <c r="F21" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="B22">
         <v>1.0609580000000001</v>
@@ -2664,12 +2676,12 @@
         <v>0.67499299999999995</v>
       </c>
       <c r="F22" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="B23">
         <v>1.0313110000000001</v>
@@ -2684,12 +2696,12 @@
         <v>0.65337999999999996</v>
       </c>
       <c r="F23" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B24">
         <v>1.0733569999999999</v>
@@ -2704,12 +2716,12 @@
         <v>0.67685899999999999</v>
       </c>
       <c r="F24" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B25">
         <v>1.0565990000000001</v>
@@ -2724,12 +2736,12 @@
         <v>0.67277600000000004</v>
       </c>
       <c r="F25" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B26">
         <v>1.075323</v>
@@ -2744,12 +2756,12 @@
         <v>0.68261499999999997</v>
       </c>
       <c r="F26" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B27">
         <v>1.072684</v>
@@ -2764,12 +2776,12 @@
         <v>0.68080600000000002</v>
       </c>
       <c r="F27" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B28">
         <v>1.057283</v>
@@ -2784,12 +2796,12 @@
         <v>0.66831499999999999</v>
       </c>
       <c r="F28" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B29">
         <v>1.068657</v>
@@ -2804,12 +2816,12 @@
         <v>0.67405599999999999</v>
       </c>
       <c r="F29" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B30">
         <v>1.073078</v>
@@ -2824,12 +2836,12 @@
         <v>0.68850199999999995</v>
       </c>
       <c r="F30" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B31">
         <v>1.0656639999999999</v>
@@ -2844,12 +2856,12 @@
         <v>0.678844</v>
       </c>
       <c r="F31" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B32">
         <v>1.0670139999999999</v>
@@ -2864,12 +2876,12 @@
         <v>0.68255299999999997</v>
       </c>
       <c r="F32" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="B33">
         <v>1.0614889999999999</v>
@@ -2884,12 +2896,12 @@
         <v>0.66840100000000002</v>
       </c>
       <c r="F33" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B34">
         <v>1.064576</v>
@@ -2904,12 +2916,12 @@
         <v>0.67110300000000001</v>
       </c>
       <c r="F34" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="B35">
         <v>1.0493079999999999</v>
@@ -2924,12 +2936,12 @@
         <v>0.66575700000000004</v>
       </c>
       <c r="F35" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B36">
         <v>1.0312030000000001</v>
@@ -2944,12 +2956,12 @@
         <v>0.65908900000000004</v>
       </c>
       <c r="F36" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B37">
         <v>1.06616</v>
@@ -2964,12 +2976,12 @@
         <v>0.67663899999999999</v>
       </c>
       <c r="F37" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B38">
         <v>1.066208</v>
@@ -2984,12 +2996,12 @@
         <v>0.67477600000000004</v>
       </c>
       <c r="F38" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="B39">
         <v>1.070506</v>
@@ -3004,12 +3016,12 @@
         <v>0.674126</v>
       </c>
       <c r="F39" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="B40">
         <v>1.062473</v>
@@ -3024,12 +3036,12 @@
         <v>0.66886000000000001</v>
       </c>
       <c r="F40" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="B41">
         <v>1.060629</v>
@@ -3044,12 +3056,12 @@
         <v>0.66756300000000002</v>
       </c>
       <c r="F41" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="B42">
         <v>1.067029</v>
@@ -3064,12 +3076,12 @@
         <v>0.674875</v>
       </c>
       <c r="F42" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="B43">
         <v>1.0565249999999999</v>
@@ -3084,12 +3096,12 @@
         <v>0.66520000000000001</v>
       </c>
       <c r="F43" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="B44">
         <v>1.0593889999999999</v>
@@ -3104,12 +3116,12 @@
         <v>0.67764400000000002</v>
       </c>
       <c r="F44" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="B45">
         <v>1.0522499999999999</v>
@@ -3124,12 +3136,12 @@
         <v>0.66460200000000003</v>
       </c>
       <c r="F45" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B46">
         <v>1.048244</v>
@@ -3144,12 +3156,12 @@
         <v>0.66415800000000003</v>
       </c>
       <c r="F46" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="B47">
         <v>1.062036</v>
@@ -3164,12 +3176,12 @@
         <v>0.66490000000000005</v>
       </c>
       <c r="F47" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="B48">
         <v>1.0685100000000001</v>
@@ -3184,12 +3196,12 @@
         <v>0.67766199999999999</v>
       </c>
       <c r="F48" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B49">
         <v>1.058001</v>
@@ -3204,12 +3216,12 @@
         <v>0.66935100000000003</v>
       </c>
       <c r="F49" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="B50">
         <v>1.059858</v>
@@ -3224,12 +3236,12 @@
         <v>0.66864199999999996</v>
       </c>
       <c r="F50" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="B51">
         <v>1.0570600000000001</v>
@@ -3244,12 +3256,12 @@
         <v>0.66720999999999997</v>
       </c>
       <c r="F51" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="B52">
         <v>1.0440590000000001</v>
@@ -3264,12 +3276,12 @@
         <v>0.66092099999999998</v>
       </c>
       <c r="F52" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="B53">
         <v>1.0540609999999999</v>
@@ -3284,12 +3296,12 @@
         <v>0.667099</v>
       </c>
       <c r="F53" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B54">
         <v>1.0602739999999999</v>
@@ -3304,12 +3316,12 @@
         <v>0.66971800000000004</v>
       </c>
       <c r="F54" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="B55">
         <v>1.0898369999999999</v>
@@ -3324,12 +3336,12 @@
         <v>0.68672299999999997</v>
       </c>
       <c r="F55" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="B56">
         <v>1.053139</v>
@@ -3344,12 +3356,12 @@
         <v>0.66843799999999998</v>
       </c>
       <c r="F56" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="B57">
         <v>1.05494</v>
@@ -3364,12 +3376,12 @@
         <v>0.66249999999999998</v>
       </c>
       <c r="F57" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="B58">
         <v>1.0928089999999999</v>
@@ -3384,12 +3396,12 @@
         <v>0.69184500000000004</v>
       </c>
       <c r="F58" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="B59">
         <v>1.0423169999999999</v>
@@ -3404,12 +3416,12 @@
         <v>0.66231099999999998</v>
       </c>
       <c r="F59" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="B60">
         <v>1.0545549999999999</v>
@@ -3424,12 +3436,12 @@
         <v>0.66138699999999995</v>
       </c>
       <c r="F60" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="B61">
         <v>1.0709109999999999</v>
@@ -3444,12 +3456,12 @@
         <v>0.67357100000000003</v>
       </c>
       <c r="F61" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="B62">
         <v>1.0698589999999999</v>
@@ -3464,12 +3476,12 @@
         <v>0.67599799999999999</v>
       </c>
       <c r="F62" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="B63">
         <v>1.04267</v>
@@ -3484,12 +3496,12 @@
         <v>0.658165</v>
       </c>
       <c r="F63" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="B64">
         <v>1.05532</v>
@@ -3504,12 +3516,12 @@
         <v>0.66752900000000004</v>
       </c>
       <c r="F64" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="B65">
         <v>1.054562</v>
@@ -3524,12 +3536,12 @@
         <v>0.67284699999999997</v>
       </c>
       <c r="F65" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B66">
         <v>1.057223</v>
@@ -3544,12 +3556,12 @@
         <v>0.67558700000000005</v>
       </c>
       <c r="F66" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B67">
         <v>1.063018</v>
@@ -3564,12 +3576,12 @@
         <v>0.66738699999999995</v>
       </c>
       <c r="F67" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="B68">
         <v>1.04288</v>
@@ -3584,12 +3596,12 @@
         <v>0.66133200000000003</v>
       </c>
       <c r="F68" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="B69">
         <v>1.05874</v>
@@ -3604,12 +3616,12 @@
         <v>0.66853200000000002</v>
       </c>
       <c r="F69" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="B70">
         <v>1.0626990000000001</v>
@@ -3624,12 +3636,12 @@
         <v>0.67108400000000001</v>
       </c>
       <c r="F70" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B71">
         <v>1.0683849999999999</v>
@@ -3644,12 +3656,12 @@
         <v>0.67861899999999997</v>
       </c>
       <c r="F71" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="B72">
         <v>1.009201</v>
@@ -3664,12 +3676,12 @@
         <v>0.64124499999999995</v>
       </c>
       <c r="F72" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="B73">
         <v>1.058481</v>
@@ -3684,12 +3696,12 @@
         <v>0.66858099999999998</v>
       </c>
       <c r="F73" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="B74">
         <v>1.0644199999999999</v>
@@ -3704,12 +3716,12 @@
         <v>0.67193499999999995</v>
       </c>
       <c r="F74" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="B75">
         <v>1.0414380000000001</v>
@@ -3724,12 +3736,12 @@
         <v>0.66406699999999996</v>
       </c>
       <c r="F75" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="B76">
         <v>1.066235</v>
@@ -3744,12 +3756,12 @@
         <v>0.67296199999999995</v>
       </c>
       <c r="F76" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="B77">
         <v>1.05646</v>
@@ -3764,12 +3776,12 @@
         <v>0.67090700000000003</v>
       </c>
       <c r="F77" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="B78">
         <v>1.0547759999999999</v>
@@ -3784,12 +3796,12 @@
         <v>0.67654199999999998</v>
       </c>
       <c r="F78" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="B79">
         <v>1.0457380000000001</v>
@@ -3804,12 +3816,12 @@
         <v>0.65707000000000004</v>
       </c>
       <c r="F79" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="B80">
         <v>1.0591010000000001</v>
@@ -3824,12 +3836,12 @@
         <v>0.66736399999999996</v>
       </c>
       <c r="F80" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="B81">
         <v>1.023593</v>
@@ -3844,12 +3856,12 @@
         <v>0.65326399999999996</v>
       </c>
       <c r="F81" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="B82">
         <v>1.0578380000000001</v>
@@ -3864,12 +3876,12 @@
         <v>0.66945900000000003</v>
       </c>
       <c r="F82" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="B83">
         <v>1.065672</v>
@@ -3884,12 +3896,12 @@
         <v>0.68224399999999996</v>
       </c>
       <c r="F83" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="B84">
         <v>1.060756</v>
@@ -3904,12 +3916,12 @@
         <v>0.66976599999999997</v>
       </c>
       <c r="F84" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="B85">
         <v>1.0777909999999999</v>
@@ -3924,12 +3936,12 @@
         <v>0.67713800000000002</v>
       </c>
       <c r="F85" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="B86">
         <v>1.059731</v>
@@ -3944,12 +3956,12 @@
         <v>0.66585499999999997</v>
       </c>
       <c r="F86" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="B87">
         <v>1.0600579999999999</v>
@@ -3964,12 +3976,12 @@
         <v>0.66844499999999996</v>
       </c>
       <c r="F87" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="B88">
         <v>1.07107</v>
@@ -3984,12 +3996,12 @@
         <v>0.67978700000000003</v>
       </c>
       <c r="F88" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="B89">
         <v>1.04982</v>
@@ -4004,12 +4016,12 @@
         <v>0.66350299999999995</v>
       </c>
       <c r="F89" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="B90">
         <v>1.0240199999999999</v>
@@ -4024,12 +4036,12 @@
         <v>0.64914400000000005</v>
       </c>
       <c r="F90" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="B91">
         <v>1.0666899999999999</v>
@@ -4044,12 +4056,12 @@
         <v>0.67187200000000002</v>
       </c>
       <c r="F91" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="B92">
         <v>1.0512889999999999</v>
@@ -4064,12 +4076,12 @@
         <v>0.66541499999999998</v>
       </c>
       <c r="F92" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="B93">
         <v>1.051277</v>
@@ -4084,12 +4096,12 @@
         <v>0.66505000000000003</v>
       </c>
       <c r="F93" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="B94">
         <v>1.0475380000000001</v>
@@ -4104,12 +4116,12 @@
         <v>0.66251499999999997</v>
       </c>
       <c r="F94" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="B95">
         <v>1.058235</v>
@@ -4124,12 +4136,12 @@
         <v>0.66830900000000004</v>
       </c>
       <c r="F95" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="B96">
         <v>1.071798</v>
@@ -4144,12 +4156,12 @@
         <v>0.67922700000000003</v>
       </c>
       <c r="F96" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="B97">
         <v>1.0596699999999999</v>
@@ -4164,12 +4176,12 @@
         <v>0.67083400000000004</v>
       </c>
       <c r="F97" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="B98">
         <v>1.0687800000000001</v>
@@ -4184,12 +4196,12 @@
         <v>0.67482699999999995</v>
       </c>
       <c r="F98" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="B99">
         <v>1.0624420000000001</v>
@@ -4204,12 +4216,12 @@
         <v>0.668346</v>
       </c>
       <c r="F99" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="B100">
         <v>1.0532600000000001</v>
@@ -4224,12 +4236,12 @@
         <v>0.66628900000000002</v>
       </c>
       <c r="F100" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="B101">
         <v>1.069016</v>
@@ -4244,12 +4256,12 @@
         <v>0.67830000000000001</v>
       </c>
       <c r="F101" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="B102">
         <v>1.0563400000000001</v>
@@ -4264,12 +4276,12 @@
         <v>0.66720999999999997</v>
       </c>
       <c r="F102" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="B103">
         <v>1.063382</v>
@@ -4284,12 +4296,12 @@
         <v>0.67581199999999997</v>
       </c>
       <c r="F103" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="B104">
         <v>1.029029</v>
@@ -4304,12 +4316,12 @@
         <v>0.64955099999999999</v>
       </c>
       <c r="F104" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B105">
         <v>1.0565389999999999</v>
@@ -4324,12 +4336,12 @@
         <v>0.66456800000000005</v>
       </c>
       <c r="F105" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="B106">
         <v>1.0745119999999999</v>
@@ -4344,12 +4356,12 @@
         <v>0.67635699999999999</v>
       </c>
       <c r="F106" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="B107">
         <v>1.0594440000000001</v>
@@ -4364,12 +4376,12 @@
         <v>0.67012099999999997</v>
       </c>
       <c r="F107" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B108">
         <v>1.072668</v>
@@ -4384,12 +4396,12 @@
         <v>0.68240400000000001</v>
       </c>
       <c r="F108" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B109">
         <v>1.055361</v>
@@ -4404,12 +4416,12 @@
         <v>0.66576299999999999</v>
       </c>
       <c r="F109" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="B110">
         <v>1.047183</v>
@@ -4424,12 +4436,12 @@
         <v>0.66105400000000003</v>
       </c>
       <c r="F110" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="B111">
         <v>1.0700750000000001</v>
@@ -4444,12 +4456,12 @@
         <v>0.67716699999999996</v>
       </c>
       <c r="F111" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="B112">
         <v>1.0421530000000001</v>
@@ -4464,12 +4476,12 @@
         <v>0.65736600000000001</v>
       </c>
       <c r="F112" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="B113">
         <v>1.019039</v>
@@ -4484,12 +4496,12 @@
         <v>0.64143399999999995</v>
       </c>
       <c r="F113" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="B114">
         <v>1.061782</v>
@@ -4504,12 +4516,12 @@
         <v>0.67122999999999999</v>
       </c>
       <c r="F114" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="B115">
         <v>1.0529900000000001</v>
@@ -4524,12 +4536,12 @@
         <v>0.66149899999999995</v>
       </c>
       <c r="F115" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B116">
         <v>1.0550539999999999</v>
@@ -4544,12 +4556,12 @@
         <v>0.667489</v>
       </c>
       <c r="F116" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="B117">
         <v>1.0710329999999999</v>
@@ -4564,12 +4576,12 @@
         <v>0.67622700000000002</v>
       </c>
       <c r="F117" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="B118">
         <v>1.0492619999999999</v>
@@ -4584,12 +4596,12 @@
         <v>0.66017499999999996</v>
       </c>
       <c r="F118" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="B119">
         <v>1.0464880000000001</v>
@@ -4604,12 +4616,12 @@
         <v>0.665821</v>
       </c>
       <c r="F119" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="B120">
         <v>1.034052</v>
@@ -4624,12 +4636,12 @@
         <v>0.65479100000000001</v>
       </c>
       <c r="F120" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B121">
         <v>1.058395</v>
@@ -4644,12 +4656,12 @@
         <v>0.66720400000000002</v>
       </c>
       <c r="F121" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="B122">
         <v>1.0577859999999999</v>
@@ -4664,12 +4676,12 @@
         <v>0.66647000000000001</v>
       </c>
       <c r="F122" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="B123">
         <v>1.056319</v>
@@ -4684,12 +4696,12 @@
         <v>0.67566700000000002</v>
       </c>
       <c r="F123" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="B124">
         <v>1.0371840000000001</v>
@@ -4704,12 +4716,12 @@
         <v>0.655968</v>
       </c>
       <c r="F124" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="B125">
         <v>1.066784</v>
@@ -4724,12 +4736,12 @@
         <v>0.67768300000000004</v>
       </c>
       <c r="F125" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="B126">
         <v>1.053301</v>
@@ -4744,12 +4756,12 @@
         <v>0.66036700000000004</v>
       </c>
       <c r="F126" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="B127">
         <v>1.066263</v>
@@ -4764,12 +4776,12 @@
         <v>0.67700899999999997</v>
       </c>
       <c r="F127" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="B128">
         <v>1.0564880000000001</v>
@@ -4784,12 +4796,12 @@
         <v>0.67002300000000004</v>
       </c>
       <c r="F128" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="B129">
         <v>1.0543169999999999</v>
@@ -4804,12 +4816,12 @@
         <v>0.66320699999999999</v>
       </c>
       <c r="F129" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="B130">
         <v>1.0446200000000001</v>
@@ -4824,12 +4836,12 @@
         <v>0.66389100000000001</v>
       </c>
       <c r="F130" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="B131">
         <v>1.060872</v>
@@ -4844,12 +4856,12 @@
         <v>0.66846799999999995</v>
       </c>
       <c r="F131" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="B132">
         <v>1.0800609999999999</v>
@@ -4864,12 +4876,12 @@
         <v>0.677566</v>
       </c>
       <c r="F132" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="B133">
         <v>1.0479400000000001</v>
@@ -4884,12 +4896,12 @@
         <v>0.66401100000000002</v>
       </c>
       <c r="F133" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="B134">
         <v>1.05941</v>
@@ -4904,12 +4916,12 @@
         <v>0.67151499999999997</v>
       </c>
       <c r="F134" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B135">
         <v>1.036481</v>
@@ -4924,12 +4936,12 @@
         <v>0.65847599999999995</v>
       </c>
       <c r="F135" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="B136">
         <v>1.003851</v>
@@ -4944,12 +4956,12 @@
         <v>0.63952100000000001</v>
       </c>
       <c r="F136" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="B137">
         <v>1.0591360000000001</v>
@@ -4964,12 +4976,12 @@
         <v>0.67156400000000005</v>
       </c>
       <c r="F137" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="B138">
         <v>1.069105</v>
@@ -4984,12 +4996,12 @@
         <v>0.67766599999999999</v>
       </c>
       <c r="F138" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="B139">
         <v>1.03999</v>
@@ -5004,12 +5016,12 @@
         <v>0.65671599999999997</v>
       </c>
       <c r="F139" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="B140">
         <v>1.039984</v>
@@ -5024,12 +5036,12 @@
         <v>0.65579500000000002</v>
       </c>
       <c r="F140" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="B141">
         <v>1.039936</v>
@@ -5044,12 +5056,12 @@
         <v>0.65578400000000003</v>
       </c>
       <c r="F141" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="B142">
         <v>1.0399389999999999</v>
@@ -5064,12 +5076,12 @@
         <v>0.65582200000000002</v>
       </c>
       <c r="F142" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="B143">
         <v>1.039936</v>
@@ -5084,12 +5096,12 @@
         <v>0.65581100000000003</v>
       </c>
       <c r="F143" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="B144">
         <v>1.0399290000000001</v>
@@ -5104,12 +5116,12 @@
         <v>0.65557799999999999</v>
       </c>
       <c r="F144" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="B145">
         <v>1.0399640000000001</v>
@@ -5124,12 +5136,12 @@
         <v>0.655806</v>
       </c>
       <c r="F145" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="B146">
         <v>1.040411</v>
@@ -5144,12 +5156,12 @@
         <v>0.66066400000000003</v>
       </c>
       <c r="F146" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="B147">
         <v>1.0432509999999999</v>
@@ -5164,12 +5176,12 @@
         <v>0.66962500000000003</v>
       </c>
       <c r="F147" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="B148">
         <v>1.0399449999999999</v>
@@ -5184,12 +5196,12 @@
         <v>0.65578400000000003</v>
       </c>
       <c r="F148" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="B149">
         <v>1.039955</v>
@@ -5204,12 +5216,12 @@
         <v>0.65576199999999996</v>
       </c>
       <c r="F149" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="B150">
         <v>1.0400670000000001</v>
@@ -5224,12 +5236,12 @@
         <v>0.655806</v>
       </c>
       <c r="F150" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="B151">
         <v>0.98404000000000003</v>
@@ -5244,12 +5256,12 @@
         <v>0.62183200000000005</v>
       </c>
       <c r="F151" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="B152">
         <v>1.0399400000000001</v>
@@ -5264,12 +5276,12 @@
         <v>0.65577300000000005</v>
       </c>
       <c r="F152" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="B153">
         <v>1.0399510000000001</v>
@@ -5284,12 +5296,12 @@
         <v>0.65558899999999998</v>
       </c>
       <c r="F153" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="B154">
         <v>1.0575270000000001</v>
@@ -5304,12 +5316,12 @@
         <v>0.66915199999999997</v>
       </c>
       <c r="F154" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="B155">
         <v>0.98472199999999999</v>
@@ -5324,12 +5336,12 @@
         <v>0.62616499999999997</v>
       </c>
       <c r="F155" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="B156">
         <v>1.0588820000000001</v>
@@ -5344,12 +5356,12 @@
         <v>0.67082600000000003</v>
       </c>
       <c r="F156" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="B157">
         <v>1.0653619999999999</v>
@@ -5364,12 +5376,12 @@
         <v>0.67403100000000005</v>
       </c>
       <c r="F157" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="B158">
         <v>1.04508</v>
@@ -5384,12 +5396,12 @@
         <v>0.66148300000000004</v>
       </c>
       <c r="F158" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="B159">
         <v>1.0686420000000001</v>
@@ -5404,12 +5416,12 @@
         <v>0.67710700000000001</v>
       </c>
       <c r="F159" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="B160">
         <v>1.065421</v>
@@ -5424,12 +5436,12 @@
         <v>0.67336300000000004</v>
       </c>
       <c r="F160" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="B161">
         <v>1.0444389999999999</v>
@@ -5444,12 +5456,12 @@
         <v>0.66105000000000003</v>
       </c>
       <c r="F161" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="B162">
         <v>1.00186</v>
@@ -5464,12 +5476,12 @@
         <v>0.63401799999999997</v>
       </c>
       <c r="F162" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="B163">
         <v>1.043434</v>
@@ -5484,12 +5496,12 @@
         <v>0.663628</v>
       </c>
       <c r="F163" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="B164">
         <v>1.051204</v>
@@ -5504,12 +5516,12 @@
         <v>0.66843200000000003</v>
       </c>
       <c r="F164" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="B165">
         <v>1.072916</v>
@@ -5524,12 +5536,12 @@
         <v>0.67705300000000002</v>
       </c>
       <c r="F165" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="B166">
         <v>1.0428710000000001</v>
@@ -5544,12 +5556,12 @@
         <v>0.66176199999999996</v>
       </c>
       <c r="F166" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="B167">
         <v>1.055766</v>
@@ -5564,12 +5576,12 @@
         <v>0.66640100000000002</v>
       </c>
       <c r="F167" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="B168">
         <v>1.0599400000000001</v>
@@ -5584,12 +5596,12 @@
         <v>0.67007799999999995</v>
       </c>
       <c r="F168" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="B169">
         <v>1.063382</v>
@@ -5604,12 +5616,12 @@
         <v>0.67044400000000004</v>
       </c>
       <c r="F169" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B170">
         <v>1.0597270000000001</v>
@@ -5624,12 +5636,12 @@
         <v>0.667574</v>
       </c>
       <c r="F170" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="B171">
         <v>1.05223</v>
@@ -5644,12 +5656,12 @@
         <v>0.66594399999999998</v>
       </c>
       <c r="F171" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="B172">
         <v>1.0622069999999999</v>
@@ -5664,12 +5676,12 @@
         <v>0.67000700000000002</v>
       </c>
       <c r="F172" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B173">
         <v>1.051258</v>
@@ -5684,12 +5696,12 @@
         <v>0.66554100000000005</v>
       </c>
       <c r="F173" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="B174">
         <v>0.99681299999999995</v>
@@ -5704,12 +5716,12 @@
         <v>0.63493200000000005</v>
       </c>
       <c r="F174" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="B175">
         <v>1.04725</v>
@@ -5724,12 +5736,12 @@
         <v>0.65658300000000003</v>
       </c>
       <c r="F175" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="B176">
         <v>1.037922</v>
@@ -5744,12 +5756,12 @@
         <v>0.65694900000000001</v>
       </c>
       <c r="F176" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="B177">
         <v>1.0625</v>
@@ -5764,12 +5776,12 @@
         <v>0.66623900000000003</v>
       </c>
       <c r="F177" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="B178">
         <v>1.0791839999999999</v>
@@ -5784,12 +5796,12 @@
         <v>0.68152100000000004</v>
       </c>
       <c r="F178" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="B179">
         <v>1.0517920000000001</v>
@@ -5804,12 +5816,12 @@
         <v>0.66526700000000005</v>
       </c>
       <c r="F179" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="B180">
         <v>1.0638799999999999</v>
@@ -5824,12 +5836,12 @@
         <v>0.67571400000000004</v>
       </c>
       <c r="F180" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="B181">
         <v>1.0575540000000001</v>
@@ -5844,12 +5856,12 @@
         <v>0.66499900000000001</v>
       </c>
       <c r="F181" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="B182">
         <v>1.0628299999999999</v>
@@ -5864,12 +5876,12 @@
         <v>0.67576700000000001</v>
       </c>
       <c r="F182" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="B183">
         <v>1.0509919999999999</v>
@@ -5884,12 +5896,12 @@
         <v>0.66576100000000005</v>
       </c>
       <c r="F183" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="B184">
         <v>1.04901</v>
@@ -5904,12 +5916,12 @@
         <v>0.663605</v>
       </c>
       <c r="F184" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="B185">
         <v>1.0704750000000001</v>
@@ -5924,12 +5936,12 @@
         <v>0.67487600000000003</v>
       </c>
       <c r="F185" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="B186">
         <v>1.053058</v>
@@ -5944,12 +5956,12 @@
         <v>0.66479900000000003</v>
       </c>
       <c r="F186" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="B187">
         <v>1.038972</v>
@@ -5964,12 +5976,12 @@
         <v>0.65948200000000001</v>
       </c>
       <c r="F187" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="B188">
         <v>1.0666679999999999</v>
@@ -5984,12 +5996,12 @@
         <v>0.67918299999999998</v>
       </c>
       <c r="F188" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="B189">
         <v>1.044306</v>
@@ -6004,12 +6016,12 @@
         <v>0.66739099999999996</v>
       </c>
       <c r="F189" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="B190">
         <v>1.085364</v>
@@ -6024,12 +6036,12 @@
         <v>0.68879500000000005</v>
       </c>
       <c r="F190" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="B191">
         <v>1.0653280000000001</v>
@@ -6044,12 +6056,12 @@
         <v>0.675315</v>
       </c>
       <c r="F191" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="B192">
         <v>1.050443</v>
@@ -6064,12 +6076,12 @@
         <v>0.65964100000000003</v>
       </c>
       <c r="F192" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="B193">
         <v>1.0174080000000001</v>
@@ -6084,12 +6096,12 @@
         <v>0.637853</v>
       </c>
       <c r="F193" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="B194">
         <v>1.059512</v>
@@ -6104,12 +6116,12 @@
         <v>0.66841899999999999</v>
       </c>
       <c r="F194" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="B195">
         <v>1.0507919999999999</v>
@@ -6124,12 +6136,12 @@
         <v>0.66408100000000003</v>
       </c>
       <c r="F195" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="B196">
         <v>1.053971</v>
@@ -6144,12 +6156,12 @@
         <v>0.66352699999999998</v>
       </c>
       <c r="F196" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="B197">
         <v>1.05389</v>
@@ -6164,12 +6176,12 @@
         <v>0.66623399999999999</v>
       </c>
       <c r="F197" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="B198">
         <v>1.0535540000000001</v>
@@ -6184,12 +6196,12 @@
         <v>0.66336300000000004</v>
       </c>
       <c r="F198" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="B199">
         <v>1.072133</v>
@@ -6204,12 +6216,12 @@
         <v>0.67689500000000002</v>
       </c>
       <c r="F199" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="B200">
         <v>1.044943</v>
@@ -6224,12 +6236,12 @@
         <v>0.65984100000000001</v>
       </c>
       <c r="F200" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="B201">
         <v>0.990232</v>
@@ -6244,12 +6256,12 @@
         <v>0.627027</v>
       </c>
       <c r="F201" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="B202">
         <v>1.058781</v>
@@ -6264,12 +6276,12 @@
         <v>0.67149199999999998</v>
       </c>
       <c r="F202" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="B203">
         <v>1.047752</v>
@@ -6284,12 +6296,12 @@
         <v>0.66585899999999998</v>
       </c>
       <c r="F203" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="B204">
         <v>1.049401</v>
@@ -6304,12 +6316,12 @@
         <v>0.66410199999999997</v>
       </c>
       <c r="F204" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="B205">
         <v>1.048926</v>
@@ -6324,12 +6336,12 @@
         <v>0.66612300000000002</v>
       </c>
       <c r="F205" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="B206">
         <v>1.029771</v>
@@ -6344,12 +6356,12 @@
         <v>0.65494200000000002</v>
       </c>
       <c r="F206" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="B207">
         <v>1.019693</v>
@@ -6364,12 +6376,12 @@
         <v>0.64383400000000002</v>
       </c>
       <c r="F207" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="B208">
         <v>1.05189</v>
@@ -6384,12 +6396,12 @@
         <v>0.66798500000000005</v>
       </c>
       <c r="F208" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="B209">
         <v>1.0436609999999999</v>
@@ -6404,12 +6416,12 @@
         <v>0.65973400000000004</v>
       </c>
       <c r="F209" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="B210">
         <v>1.0127600000000001</v>
@@ -6424,12 +6436,12 @@
         <v>0.64081900000000003</v>
       </c>
       <c r="F210" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="B211">
         <v>1.06057</v>
@@ -6444,12 +6456,12 @@
         <v>0.674543</v>
       </c>
       <c r="F211" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="B212">
         <v>1.0508759999999999</v>
@@ -6464,12 +6476,12 @@
         <v>0.66667600000000005</v>
       </c>
       <c r="F212" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="B213">
         <v>1.07</v>
@@ -6484,12 +6496,12 @@
         <v>0.67675200000000002</v>
       </c>
       <c r="F213" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="B214">
         <v>1.0323199999999999</v>
@@ -6504,12 +6516,12 @@
         <v>0.65345600000000004</v>
       </c>
       <c r="F214" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="B215">
         <v>1.050721</v>
@@ -6524,12 +6536,12 @@
         <v>0.66584399999999999</v>
       </c>
       <c r="F215" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="B216">
         <v>1.0405310000000001</v>
@@ -6544,12 +6556,12 @@
         <v>0.65778999999999999</v>
       </c>
       <c r="F216" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B217">
         <v>1.0178990000000001</v>
@@ -6564,12 +6576,12 @@
         <v>0.64397199999999999</v>
       </c>
       <c r="F217" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="B218">
         <v>1.0462830000000001</v>
@@ -6584,12 +6596,12 @@
         <v>0.66174100000000002</v>
       </c>
       <c r="F218" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="B219">
         <v>1.0430200000000001</v>
@@ -6604,12 +6616,12 @@
         <v>0.66033299999999995</v>
       </c>
       <c r="F219" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="B220">
         <v>1.0591360000000001</v>
@@ -6624,12 +6636,12 @@
         <v>0.67279500000000003</v>
       </c>
       <c r="F220" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="B221">
         <v>1.0560700000000001</v>
@@ -6644,12 +6656,12 @@
         <v>0.66837199999999997</v>
       </c>
       <c r="F221" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="B222">
         <v>1.035768</v>
@@ -6664,12 +6676,12 @@
         <v>0.65384799999999998</v>
       </c>
       <c r="F222" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="B223">
         <v>1.0147470000000001</v>
@@ -6684,12 +6696,12 @@
         <v>0.63985199999999998</v>
       </c>
       <c r="F223" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="B224">
         <v>1.0365599999999999</v>
@@ -6704,12 +6716,12 @@
         <v>0.65735200000000005</v>
       </c>
       <c r="F224" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="B225">
         <v>1.05026</v>
@@ -6724,12 +6736,12 @@
         <v>0.66172299999999995</v>
       </c>
       <c r="F225" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="B226">
         <v>1.0297000000000001</v>
@@ -6744,12 +6756,12 @@
         <v>0.65113299999999996</v>
       </c>
       <c r="F226" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="B227">
         <v>1.0456430000000001</v>
@@ -6764,12 +6776,12 @@
         <v>0.66274500000000003</v>
       </c>
       <c r="F227" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="B228">
         <v>1.0549200000000001</v>
@@ -6784,12 +6796,12 @@
         <v>0.66709399999999996</v>
       </c>
       <c r="F228" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="B229">
         <v>1.0626599999999999</v>
@@ -6804,12 +6816,12 @@
         <v>0.67017700000000002</v>
       </c>
       <c r="F229" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="B230">
         <v>1.057793</v>
@@ -6824,12 +6836,12 @@
         <v>0.67050699999999996</v>
       </c>
       <c r="F230" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="B231">
         <v>1.03745</v>
@@ -6844,12 +6856,12 @@
         <v>0.65609799999999996</v>
       </c>
       <c r="F231" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="B232">
         <v>1.065774</v>
@@ -6864,12 +6876,12 @@
         <v>0.67417800000000006</v>
       </c>
       <c r="F232" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="B233">
         <v>1.0497080000000001</v>
@@ -6884,12 +6896,12 @@
         <v>0.66890000000000005</v>
       </c>
       <c r="F233" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="B234">
         <v>1.0477510000000001</v>
@@ -6904,12 +6916,12 @@
         <v>0.661439</v>
       </c>
       <c r="F234" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="B235">
         <v>1.0143679999999999</v>
@@ -6924,12 +6936,12 @@
         <v>0.64723299999999995</v>
       </c>
       <c r="F235" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="B236">
         <v>1.015541</v>
@@ -6944,12 +6956,12 @@
         <v>0.64090800000000003</v>
       </c>
       <c r="F236" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="B237">
         <v>1.0304199999999999</v>
@@ -6964,12 +6976,12 @@
         <v>0.65225999999999995</v>
       </c>
       <c r="F237" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="B238">
         <v>1.0449409999999999</v>
@@ -6984,12 +6996,12 @@
         <v>0.66297399999999995</v>
       </c>
       <c r="F238" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="B239">
         <v>1.0079070000000001</v>
@@ -7004,12 +7016,12 @@
         <v>0.63653899999999997</v>
       </c>
       <c r="F239" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="B240">
         <v>1.070095</v>
@@ -7024,12 +7036,12 @@
         <v>0.67534300000000003</v>
       </c>
       <c r="F240" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="B241">
         <v>1.0750869999999999</v>
@@ -7044,12 +7056,12 @@
         <v>0.68388400000000005</v>
       </c>
       <c r="F241" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="B242">
         <v>1.0288459999999999</v>
@@ -7064,12 +7076,12 @@
         <v>0.65300199999999997</v>
       </c>
       <c r="F242" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="B243">
         <v>1.0541499999999999</v>
@@ -7084,12 +7096,12 @@
         <v>0.66779299999999997</v>
       </c>
       <c r="F243" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="B244">
         <v>1.0460100000000001</v>
@@ -7104,12 +7116,12 @@
         <v>0.66287200000000002</v>
       </c>
       <c r="F244" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="B245">
         <v>1.0443929999999999</v>
@@ -7124,12 +7136,12 @@
         <v>0.66185400000000005</v>
       </c>
       <c r="F245" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="B246">
         <v>1.0443750000000001</v>
@@ -7144,12 +7156,12 @@
         <v>0.66228799999999999</v>
       </c>
       <c r="F246" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="B247">
         <v>1.0410919999999999</v>
@@ -7164,12 +7176,12 @@
         <v>0.65717899999999996</v>
       </c>
       <c r="F247" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="B248">
         <v>1.0451459999999999</v>
@@ -7184,12 +7196,12 @@
         <v>0.66271500000000005</v>
       </c>
       <c r="F248" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="B249">
         <v>1.043982</v>
@@ -7204,12 +7216,12 @@
         <v>0.65626499999999999</v>
       </c>
       <c r="F249" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="B250">
         <v>1.021825</v>
@@ -7224,12 +7236,12 @@
         <v>0.64939599999999997</v>
       </c>
       <c r="F250" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="B251">
         <v>1.0535680000000001</v>
@@ -7244,12 +7256,12 @@
         <v>0.66742999999999997</v>
       </c>
       <c r="F251" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="B252">
         <v>1.040848</v>
@@ -7264,12 +7276,12 @@
         <v>0.65634700000000001</v>
       </c>
       <c r="F252" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="B253">
         <v>1.03803</v>
@@ -7284,12 +7296,12 @@
         <v>0.65468899999999997</v>
       </c>
       <c r="F253" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="B254">
         <v>1.024756</v>
@@ -7304,12 +7316,12 @@
         <v>0.64946499999999996</v>
       </c>
       <c r="F254" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="B255">
         <v>1.0205230000000001</v>
@@ -7324,12 +7336,12 @@
         <v>0.64911200000000002</v>
       </c>
       <c r="F255" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="B256">
         <v>1.0201290000000001</v>
@@ -7344,12 +7356,12 @@
         <v>0.645092</v>
       </c>
       <c r="F256" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="B257">
         <v>1.0239659999999999</v>
@@ -7364,12 +7376,12 @@
         <v>0.64562600000000003</v>
       </c>
       <c r="F257" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="258" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="B258">
         <v>1.03067</v>
@@ -7384,12 +7396,12 @@
         <v>0.65104099999999998</v>
       </c>
       <c r="F258" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="259" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="B259">
         <v>1.0670440000000001</v>
@@ -7404,12 +7416,12 @@
         <v>0.67335400000000001</v>
       </c>
       <c r="F259" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="260" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="B260">
         <v>1.0494460000000001</v>
@@ -7424,12 +7436,12 @@
         <v>0.66324499999999997</v>
       </c>
       <c r="F260" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="261" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="B261">
         <v>1.045078</v>
@@ -7444,12 +7456,12 @@
         <v>0.66130699999999998</v>
       </c>
       <c r="F261" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="B262">
         <v>1.0382169999999999</v>
@@ -7464,12 +7476,12 @@
         <v>0.65939499999999995</v>
       </c>
       <c r="F262" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="263" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="B263">
         <v>1.059518</v>
@@ -7484,12 +7496,12 @@
         <v>0.67146899999999998</v>
       </c>
       <c r="F263" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="B264">
         <v>1.01328</v>
@@ -7504,12 +7516,12 @@
         <v>0.64109899999999997</v>
       </c>
       <c r="F264" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="265" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="B265">
         <v>1.0274970000000001</v>
@@ -7524,12 +7536,12 @@
         <v>0.65292600000000001</v>
       </c>
       <c r="F265" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
     </row>
     <row r="266" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="B266">
         <v>1.0155000000000001</v>
@@ -7544,12 +7556,12 @@
         <v>0.64294499999999999</v>
       </c>
       <c r="F266" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="267" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="B267">
         <v>1.0168440000000001</v>
@@ -7564,12 +7576,12 @@
         <v>0.64474699999999996</v>
       </c>
       <c r="F267" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="268" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="B268">
         <v>1.079612</v>
@@ -7584,12 +7596,12 @@
         <v>0.68324799999999997</v>
       </c>
       <c r="F268" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="269" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="B269">
         <v>1.0176190000000001</v>
@@ -7604,12 +7616,12 @@
         <v>0.64353199999999999</v>
       </c>
       <c r="F269" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="270" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="B270">
         <v>1.0418499999999999</v>
@@ -7624,12 +7636,12 @@
         <v>0.656752</v>
       </c>
       <c r="F270" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
     </row>
     <row r="271" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="B271">
         <v>1.0295909999999999</v>
@@ -7644,12 +7656,12 @@
         <v>0.65359800000000001</v>
       </c>
       <c r="F271" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="272" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="B272">
         <v>1.0325500000000001</v>
@@ -7664,12 +7676,12 @@
         <v>0.65314799999999995</v>
       </c>
       <c r="F272" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="273" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="B273">
         <v>1.070249</v>
@@ -7684,12 +7696,12 @@
         <v>0.68303700000000001</v>
       </c>
       <c r="F273" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="274" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="B274">
         <v>1.016178</v>
@@ -7704,12 +7716,12 @@
         <v>0.64122299999999999</v>
       </c>
       <c r="F274" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="275" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="B275">
         <v>1.04843</v>
@@ -7724,12 +7736,12 @@
         <v>0.66110899999999995</v>
       </c>
       <c r="F275" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
     </row>
     <row r="276" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="B276">
         <v>1.0637559999999999</v>
@@ -7744,12 +7756,12 @@
         <v>0.67239700000000002</v>
       </c>
       <c r="F276" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="277" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="B277">
         <v>1.0270189999999999</v>
@@ -7764,12 +7776,12 @@
         <v>0.65019899999999997</v>
       </c>
       <c r="F277" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="278" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="B278">
         <v>1.056365</v>
@@ -7784,12 +7796,12 @@
         <v>0.66806100000000002</v>
       </c>
       <c r="F278" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
     </row>
     <row r="279" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="B279">
         <v>1.0352170000000001</v>
@@ -7804,12 +7816,12 @@
         <v>0.64993000000000001</v>
       </c>
       <c r="F279" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
     </row>
     <row r="280" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="B280">
         <v>1.0350790000000001</v>
@@ -7824,12 +7836,12 @@
         <v>0.65781000000000001</v>
       </c>
       <c r="F280" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
     </row>
     <row r="281" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="B281">
         <v>1.0159130000000001</v>
@@ -7844,12 +7856,12 @@
         <v>0.64292099999999996</v>
       </c>
       <c r="F281" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="282" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="B282">
         <v>0.96823000000000004</v>
@@ -7864,12 +7876,12 @@
         <v>0.61288699999999996</v>
       </c>
       <c r="F282" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
     </row>
     <row r="283" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="B283">
         <v>1.0214589999999999</v>
@@ -7884,12 +7896,12 @@
         <v>0.64708900000000003</v>
       </c>
       <c r="F283" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="284" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="B284">
         <v>1.029277</v>
@@ -7904,12 +7916,12 @@
         <v>0.64499300000000004</v>
       </c>
       <c r="F284" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="285" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="B285">
         <v>1.0317480000000001</v>
@@ -7924,12 +7936,12 @@
         <v>0.653416</v>
       </c>
       <c r="F285" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="286" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="B286">
         <v>0.99082199999999998</v>
@@ -7944,12 +7956,12 @@
         <v>0.62363900000000005</v>
       </c>
       <c r="F286" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
     </row>
     <row r="287" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="B287">
         <v>1.0323599999999999</v>
@@ -7964,12 +7976,12 @@
         <v>0.65506299999999995</v>
       </c>
       <c r="F287" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="288" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="B288">
         <v>1.0014810000000001</v>
@@ -7984,12 +7996,12 @@
         <v>0.63417599999999996</v>
       </c>
       <c r="F288" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="289" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="B289">
         <v>1.019736</v>
@@ -8004,12 +8016,12 @@
         <v>0.64638099999999998</v>
       </c>
       <c r="F289" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="B290">
         <v>1.032143</v>
@@ -8024,12 +8036,12 @@
         <v>0.64881800000000001</v>
       </c>
       <c r="F290" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
     </row>
     <row r="291" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="B291">
         <v>1.05304</v>
@@ -8044,12 +8056,12 @@
         <v>0.66786000000000001</v>
       </c>
       <c r="F291" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="292" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="B292">
         <v>1.0329330000000001</v>
@@ -8064,12 +8076,12 @@
         <v>0.65549999999999997</v>
       </c>
       <c r="F292" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="293" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="B293">
         <v>1.03274</v>
@@ -8084,12 +8096,12 @@
         <v>0.65202700000000002</v>
       </c>
       <c r="F293" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="B294">
         <v>1.0228740000000001</v>
@@ -8104,12 +8116,12 @@
         <v>0.64759</v>
       </c>
       <c r="F294" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="B295">
         <v>1.077013</v>
@@ -8124,12 +8136,12 @@
         <v>0.68293800000000005</v>
       </c>
       <c r="F295" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
     </row>
     <row r="296" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="B296">
         <v>1.0620700000000001</v>
@@ -8144,12 +8156,12 @@
         <v>0.67120299999999999</v>
       </c>
       <c r="F296" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="297" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="B297">
         <v>1.0417810000000001</v>
@@ -8164,12 +8176,12 @@
         <v>0.66213599999999995</v>
       </c>
       <c r="F297" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
     </row>
     <row r="298" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="B298">
         <v>1.0311060000000001</v>
@@ -8184,12 +8196,12 @@
         <v>0.65039100000000005</v>
       </c>
       <c r="F298" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="299" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="B299">
         <v>1.016527</v>
@@ -8204,12 +8216,12 @@
         <v>0.64075300000000002</v>
       </c>
       <c r="F299" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="300" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="B300">
         <v>1.05935</v>
@@ -8224,12 +8236,12 @@
         <v>0.66721200000000003</v>
       </c>
       <c r="F300" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
     </row>
     <row r="301" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="B301">
         <v>1.021833</v>
@@ -8244,12 +8256,12 @@
         <v>0.64777099999999999</v>
       </c>
       <c r="F301" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="302" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="B302">
         <v>1.03983</v>
@@ -8264,12 +8276,12 @@
         <v>0.65852900000000003</v>
       </c>
       <c r="F302" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
     </row>
     <row r="303" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="B303">
         <v>0.99307199999999995</v>
@@ -8284,12 +8296,12 @@
         <v>0.62707000000000002</v>
       </c>
       <c r="F303" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="304" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="B304">
         <v>1.02397</v>
@@ -8304,12 +8316,12 @@
         <v>0.65419099999999997</v>
       </c>
       <c r="F304" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="305" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="B305">
         <v>1.0356099999999999</v>
@@ -8324,12 +8336,12 @@
         <v>0.65547900000000003</v>
       </c>
       <c r="F305" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="306" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="B306">
         <v>1.033142</v>
@@ -8344,12 +8356,12 @@
         <v>0.65345799999999998</v>
       </c>
       <c r="F306" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="307" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="B307">
         <v>1.012413</v>
@@ -8364,12 +8376,12 @@
         <v>0.63717100000000004</v>
       </c>
       <c r="F307" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="308" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="B308">
         <v>1.0512840000000001</v>
@@ -8384,12 +8396,12 @@
         <v>0.66785399999999995</v>
       </c>
       <c r="F308" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
     </row>
     <row r="309" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="B309">
         <v>1.007409</v>
@@ -8404,12 +8416,12 @@
         <v>0.63892099999999996</v>
       </c>
       <c r="F309" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="310" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="B310">
         <v>1.0255099999999999</v>
@@ -8424,12 +8436,12 @@
         <v>0.64928300000000005</v>
       </c>
       <c r="F310" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
     </row>
     <row r="311" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="B311">
         <v>1.0402709999999999</v>
@@ -8444,12 +8456,12 @@
         <v>0.65252900000000003</v>
       </c>
       <c r="F311" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="312" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="B312">
         <v>0.99009599999999998</v>
@@ -8464,12 +8476,12 @@
         <v>0.62758999999999998</v>
       </c>
       <c r="F312" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="313" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="B313">
         <v>1.0039070000000001</v>
@@ -8484,12 +8496,12 @@
         <v>0.63595100000000004</v>
       </c>
       <c r="F313" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="314" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="B314">
         <v>1.0172300000000001</v>
@@ -8504,12 +8516,12 @@
         <v>0.64178000000000002</v>
       </c>
       <c r="F314" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="315" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="B315">
         <v>1.040578</v>
@@ -8524,12 +8536,12 @@
         <v>0.66216600000000003</v>
       </c>
       <c r="F315" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
     </row>
     <row r="316" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="B316">
         <v>1.0133719999999999</v>
@@ -8544,12 +8556,12 @@
         <v>0.63963700000000001</v>
       </c>
       <c r="F316" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="317" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="B317">
         <v>1.032848</v>
@@ -8564,12 +8576,12 @@
         <v>0.65525</v>
       </c>
       <c r="F317" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="318" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="B318">
         <v>1.030689</v>
@@ -8584,12 +8596,12 @@
         <v>0.65236499999999997</v>
       </c>
       <c r="F318" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
     </row>
     <row r="319" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="B319">
         <v>1.017231</v>
@@ -8604,12 +8616,12 @@
         <v>0.64663300000000001</v>
       </c>
       <c r="F319" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="320" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="B320">
         <v>1.0290429999999999</v>
@@ -8624,12 +8636,12 @@
         <v>0.64829800000000004</v>
       </c>
       <c r="F320" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="321" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="B321">
         <v>0.98892100000000005</v>
@@ -8644,12 +8656,12 @@
         <v>0.62849500000000003</v>
       </c>
       <c r="F321" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
     </row>
     <row r="322" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="B322">
         <v>1.019406</v>
@@ -8664,12 +8676,12 @@
         <v>0.64367300000000005</v>
       </c>
       <c r="F322" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
     </row>
     <row r="323" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="B323">
         <v>1.044001</v>
@@ -8684,12 +8696,12 @@
         <v>0.65842900000000004</v>
       </c>
       <c r="F323" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
     </row>
     <row r="324" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="B324">
         <v>1.01885</v>
@@ -8704,12 +8716,12 @@
         <v>0.64699899999999999</v>
       </c>
       <c r="F324" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="325" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="B325">
         <v>0.98538499999999996</v>
@@ -8724,12 +8736,12 @@
         <v>0.62530699999999995</v>
       </c>
       <c r="F325" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="326" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="B326">
         <v>1.0165090000000001</v>
@@ -8744,12 +8756,12 @@
         <v>0.64271199999999995</v>
       </c>
       <c r="F326" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
     </row>
     <row r="327" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="B327">
         <v>1.0165329999999999</v>
@@ -8764,12 +8776,12 @@
         <v>0.64437599999999995</v>
       </c>
       <c r="F327" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
     </row>
     <row r="328" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="B328">
         <v>1.0174380000000001</v>
@@ -8784,12 +8796,12 @@
         <v>0.64384200000000003</v>
       </c>
       <c r="F328" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="329" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="B329">
         <v>1.0129900000000001</v>
@@ -8804,12 +8816,12 @@
         <v>0.64162600000000003</v>
       </c>
       <c r="F329" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="330" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="B330">
         <v>1.02504</v>
@@ -8824,12 +8836,12 @@
         <v>0.65079900000000002</v>
       </c>
       <c r="F330" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="331" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="B331">
         <v>1.001509</v>
@@ -8844,12 +8856,12 @@
         <v>0.63190400000000002</v>
       </c>
       <c r="F331" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="332" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="B332">
         <v>1.0369459999999999</v>
@@ -8864,12 +8876,12 @@
         <v>0.65960600000000003</v>
       </c>
       <c r="F332" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
     </row>
     <row r="333" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="B333">
         <v>0.99493799999999999</v>
@@ -8884,12 +8896,12 @@
         <v>0.62961100000000003</v>
       </c>
       <c r="F333" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
     </row>
     <row r="334" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="B334">
         <v>0.97499599999999997</v>
@@ -8904,12 +8916,12 @@
         <v>0.60998300000000005</v>
       </c>
       <c r="F334" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
     </row>
     <row r="335" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="B335">
         <v>1.014691</v>
@@ -8924,12 +8936,12 @@
         <v>0.64002800000000004</v>
       </c>
       <c r="F335" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="336" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="B336">
         <v>1.014297</v>
@@ -8944,12 +8956,12 @@
         <v>0.64420599999999995</v>
       </c>
       <c r="F336" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
     </row>
     <row r="337" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="B337">
         <v>1.0103899999999999</v>
@@ -8964,12 +8976,12 @@
         <v>0.63778100000000004</v>
       </c>
       <c r="F337" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="338" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="B338">
         <v>1.032877</v>
@@ -8984,12 +8996,12 @@
         <v>0.65840100000000001</v>
       </c>
       <c r="F338" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="339" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="B339">
         <v>1.005558</v>
@@ -9004,12 +9016,12 @@
         <v>0.636737</v>
       </c>
       <c r="F339" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="340" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="B340">
         <v>1.008367</v>
@@ -9024,12 +9036,12 @@
         <v>0.64093299999999997</v>
       </c>
       <c r="F340" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
     </row>
     <row r="341" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="B341">
         <v>1.002332</v>
@@ -9044,12 +9056,12 @@
         <v>0.63807000000000003</v>
       </c>
       <c r="F341" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
     </row>
     <row r="342" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="B342">
         <v>1.0434349999999999</v>
@@ -9064,12 +9076,12 @@
         <v>0.65979500000000002</v>
       </c>
       <c r="F342" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="343" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="B343">
         <v>0.99773800000000001</v>
@@ -9084,12 +9096,12 @@
         <v>0.63442200000000004</v>
       </c>
       <c r="F343" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="344" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="B344">
         <v>1.0275190000000001</v>
@@ -9104,12 +9116,12 @@
         <v>0.65256199999999998</v>
       </c>
       <c r="F344" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
     </row>
     <row r="345" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="B345">
         <v>0.98973100000000003</v>
@@ -9124,12 +9136,12 @@
         <v>0.62793900000000002</v>
       </c>
       <c r="F345" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="346" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="B346">
         <v>1.0151539999999999</v>
@@ -9144,12 +9156,12 @@
         <v>0.64816700000000005</v>
       </c>
       <c r="F346" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="347" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="B347">
         <v>1.0298989999999999</v>
@@ -9164,12 +9176,12 @@
         <v>0.65149800000000002</v>
       </c>
       <c r="F347" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="348" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="B348">
         <v>0.97920099999999999</v>
@@ -9184,12 +9196,12 @@
         <v>0.62347300000000005</v>
       </c>
       <c r="F348" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="349" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="B349">
         <v>0.99785699999999999</v>
@@ -9204,12 +9216,12 @@
         <v>0.63249999999999995</v>
       </c>
       <c r="F349" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="350" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="B350">
         <v>0.99846999999999997</v>
@@ -9224,12 +9236,12 @@
         <v>0.63405500000000004</v>
       </c>
       <c r="F350" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="351" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="B351">
         <v>1.0240149999999999</v>
@@ -9244,12 +9256,12 @@
         <v>0.64932000000000001</v>
       </c>
       <c r="F351" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
     </row>
     <row r="352" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="B352">
         <v>1.0136419999999999</v>
@@ -9264,12 +9276,12 @@
         <v>0.63941400000000004</v>
       </c>
       <c r="F352" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
     </row>
     <row r="353" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="B353">
         <v>1.017711</v>
@@ -9284,12 +9296,12 @@
         <v>0.64626399999999995</v>
       </c>
       <c r="F353" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
     </row>
     <row r="354" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="B354">
         <v>1.002723</v>
@@ -9304,12 +9316,12 @@
         <v>0.63641899999999996</v>
       </c>
       <c r="F354" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
     </row>
     <row r="355" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="B355">
         <v>0.97970000000000002</v>
@@ -9324,12 +9336,12 @@
         <v>0.62147200000000002</v>
       </c>
       <c r="F355" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
     </row>
     <row r="356" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="B356">
         <v>1.0173479999999999</v>
@@ -9344,12 +9356,12 @@
         <v>0.64378000000000002</v>
       </c>
       <c r="F356" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
     </row>
     <row r="357" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="B357">
         <v>0.98057799999999995</v>
@@ -9364,12 +9376,12 @@
         <v>0.62246000000000001</v>
       </c>
       <c r="F357" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
     </row>
     <row r="358" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="B358">
         <v>1.0420020000000001</v>
@@ -9384,12 +9396,12 @@
         <v>0.66997099999999998</v>
       </c>
       <c r="F358" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="359" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="B359">
         <v>1.023685</v>
@@ -9404,12 +9416,12 @@
         <v>0.64446599999999998</v>
       </c>
       <c r="F359" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
     </row>
     <row r="360" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="B360">
         <v>1.0508569999999999</v>
@@ -9424,12 +9436,12 @@
         <v>0.66519099999999998</v>
       </c>
       <c r="F360" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
     </row>
     <row r="361" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="B361">
         <v>0.99268400000000001</v>
@@ -9444,12 +9456,12 @@
         <v>0.63014800000000004</v>
       </c>
       <c r="F361" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="362" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="B362">
         <v>1.0822750000000001</v>
@@ -9464,12 +9476,12 @@
         <v>0.68128200000000005</v>
       </c>
       <c r="F362" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="363" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="B363">
         <v>0.99639</v>
@@ -9484,12 +9496,12 @@
         <v>0.63279399999999997</v>
       </c>
       <c r="F363" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
     </row>
     <row r="364" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="B364">
         <v>1.0210189999999999</v>
@@ -9504,12 +9516,12 @@
         <v>0.64824899999999996</v>
       </c>
       <c r="F364" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="365" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="B365">
         <v>0.99593600000000004</v>
@@ -9524,12 +9536,12 @@
         <v>0.62787999999999999</v>
       </c>
       <c r="F365" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
     </row>
     <row r="366" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="B366">
         <v>1.0441240000000001</v>
@@ -9544,12 +9556,12 @@
         <v>0.65940399999999999</v>
       </c>
       <c r="F366" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
     </row>
     <row r="367" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="B367">
         <v>1.0960909999999999</v>
@@ -9564,12 +9576,12 @@
         <v>0.69905399999999995</v>
       </c>
       <c r="F367" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
     </row>
     <row r="368" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="B368">
         <v>1.0698270000000001</v>
@@ -9584,12 +9596,12 @@
         <v>0.67983099999999996</v>
       </c>
       <c r="F368" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="369" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="B369">
         <v>1.060473</v>
@@ -9604,12 +9616,12 @@
         <v>0.67909299999999995</v>
       </c>
       <c r="F369" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="370" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="B370">
         <v>1.0542940000000001</v>
@@ -9624,12 +9636,12 @@
         <v>0.66925999999999997</v>
       </c>
       <c r="F370" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="371" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="B371">
         <v>1.0581130000000001</v>
@@ -9644,12 +9656,12 @@
         <v>0.67275600000000002</v>
       </c>
       <c r="F371" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="372" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="B372">
         <v>0.94916199999999995</v>
@@ -9664,12 +9676,12 @@
         <v>0.59848400000000002</v>
       </c>
       <c r="F372" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
     </row>
     <row r="373" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="B373">
         <v>1.0791299999999999</v>
@@ -9684,12 +9696,12 @@
         <v>0.685114</v>
       </c>
       <c r="F373" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
     </row>
     <row r="374" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="B374">
         <v>0.98620699999999994</v>
@@ -9704,12 +9716,12 @@
         <v>0.62529299999999999</v>
       </c>
       <c r="F374" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="375" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="B375">
         <v>1.0807690000000001</v>
@@ -9724,12 +9736,12 @@
         <v>0.68327599999999999</v>
       </c>
       <c r="F375" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
     </row>
     <row r="376" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="B376">
         <v>1.064867</v>
@@ -9744,12 +9756,12 @@
         <v>0.67142999999999997</v>
       </c>
       <c r="F376" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="377" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="B377">
         <v>1.0126059999999999</v>
@@ -9764,12 +9776,12 @@
         <v>0.64119999999999999</v>
       </c>
       <c r="F377" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="378" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="B378">
         <v>1.075663</v>
@@ -9784,12 +9796,12 @@
         <v>0.687612</v>
       </c>
       <c r="F378" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="379" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="B379">
         <v>1.076638</v>
@@ -9804,12 +9816,12 @@
         <v>0.68806199999999995</v>
       </c>
       <c r="F379" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="380" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="B380">
         <v>1.0543260000000001</v>
@@ -9824,12 +9836,12 @@
         <v>0.66971999999999998</v>
       </c>
       <c r="F380" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="381" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="B381">
         <v>1.04399</v>
@@ -9844,12 +9856,12 @@
         <v>0.66030100000000003</v>
       </c>
       <c r="F381" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="382" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="B382">
         <v>1.0639099999999999</v>
@@ -9864,12 +9876,12 @@
         <v>0.67582600000000004</v>
       </c>
       <c r="F382" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="383" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="B383">
         <v>1.0736559999999999</v>
@@ -9884,12 +9896,12 @@
         <v>0.68309799999999998</v>
       </c>
       <c r="F383" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="384" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="B384">
         <v>1.045633</v>
@@ -9904,12 +9916,12 @@
         <v>0.66065300000000005</v>
       </c>
       <c r="F384" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
     </row>
     <row r="385" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="B385">
         <v>1.0639609999999999</v>
@@ -9924,12 +9936,12 @@
         <v>0.67652999999999996</v>
       </c>
       <c r="F385" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="386" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="B386">
         <v>1.066068</v>
@@ -9944,12 +9956,12 @@
         <v>0.67593000000000003</v>
       </c>
       <c r="F386" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="387" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="B387">
         <v>1.066068</v>
@@ -9964,12 +9976,12 @@
         <v>0.67757000000000001</v>
       </c>
       <c r="F387" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="388" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="B388">
         <v>1.066019</v>
@@ -9984,12 +9996,12 @@
         <v>0.67761800000000005</v>
       </c>
       <c r="F388" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="389" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="B389">
         <v>1.0553459999999999</v>
@@ -10004,12 +10016,12 @@
         <v>0.67131799999999997</v>
       </c>
       <c r="F389" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="390" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="B390">
         <v>1.035482</v>
@@ -10024,12 +10036,12 @@
         <v>0.65432999999999997</v>
       </c>
       <c r="F390" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="391" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="B391">
         <v>1.0263720000000001</v>
@@ -10044,12 +10056,12 @@
         <v>0.64394200000000001</v>
       </c>
       <c r="F391" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="392" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="B392">
         <v>1.0620449999999999</v>
@@ -10064,12 +10076,12 @@
         <v>0.67350200000000005</v>
       </c>
       <c r="F392" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="393" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="B393">
         <v>1.0502499999999999</v>
@@ -10084,12 +10096,12 @@
         <v>0.66988999999999999</v>
       </c>
       <c r="F393" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="394" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="B394">
         <v>1.0502499999999999</v>
@@ -10104,12 +10116,12 @@
         <v>0.66989299999999996</v>
       </c>
       <c r="F394" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="395" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="B395">
         <v>1.0502499999999999</v>
@@ -10124,12 +10136,12 @@
         <v>0.66988000000000003</v>
       </c>
       <c r="F395" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="396" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="B396">
         <v>1.0502400000000001</v>
@@ -10144,12 +10156,12 @@
         <v>0.66987699999999994</v>
       </c>
       <c r="F396" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="397" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="B397">
         <v>1.0498099999999999</v>
@@ -10164,12 +10176,12 @@
         <v>0.67389699999999997</v>
       </c>
       <c r="F397" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="398" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="B398">
         <v>1.0498149999999999</v>
@@ -10184,12 +10196,12 @@
         <v>0.67391100000000004</v>
       </c>
       <c r="F398" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="399" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="B399">
         <v>1.0493110000000001</v>
@@ -10204,12 +10216,12 @@
         <v>0.66633100000000001</v>
       </c>
       <c r="F399" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="400" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="B400">
         <v>1.0475559999999999</v>
@@ -10224,12 +10236,12 @@
         <v>0.67247500000000004</v>
       </c>
       <c r="F400" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="401" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="B401">
         <v>1.0480320000000001</v>
@@ -10244,12 +10256,12 @@
         <v>0.66729400000000005</v>
       </c>
       <c r="F401" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="402" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="B402">
         <v>1.068389</v>
@@ -10264,12 +10276,12 @@
         <v>0.68165900000000001</v>
       </c>
       <c r="F402" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="403" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="B403">
         <v>1.047401</v>
@@ -10284,12 +10296,12 @@
         <v>0.66646499999999997</v>
       </c>
       <c r="F403" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="404" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="B404">
         <v>1.0788150000000001</v>
@@ -10304,12 +10316,12 @@
         <v>0.687751</v>
       </c>
       <c r="F404" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="405" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="B405">
         <v>1.0701929999999999</v>
@@ -10324,12 +10336,12 @@
         <v>0.682222</v>
       </c>
       <c r="F405" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
     </row>
     <row r="406" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="B406">
         <v>0.96725000000000005</v>
@@ -10344,12 +10356,12 @@
         <v>0.61208600000000002</v>
       </c>
       <c r="F406" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
     </row>
     <row r="407" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="B407">
         <v>1.0639909999999999</v>
@@ -10364,12 +10376,12 @@
         <v>0.67267100000000002</v>
       </c>
       <c r="F407" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="408" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="B408">
         <v>1.0662830000000001</v>
@@ -10384,12 +10396,12 @@
         <v>0.67793599999999998</v>
       </c>
       <c r="F408" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="409" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="B409">
         <v>1.078508</v>
@@ -10404,12 +10416,12 @@
         <v>0.68406199999999995</v>
       </c>
       <c r="F409" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="410" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="B410">
         <v>1.0698620000000001</v>
@@ -10424,12 +10436,12 @@
         <v>0.67833500000000002</v>
       </c>
       <c r="F410" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="411" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="B411">
         <v>1.066684</v>
@@ -10444,12 +10456,12 @@
         <v>0.67410400000000004</v>
       </c>
       <c r="F411" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="412" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="B412">
         <v>1.094924</v>
@@ -10464,12 +10476,12 @@
         <v>0.69739099999999998</v>
       </c>
       <c r="F412" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="413" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="B413">
         <v>1.0652870000000001</v>
@@ -10484,12 +10496,12 @@
         <v>0.67875300000000005</v>
       </c>
       <c r="F413" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
     </row>
     <row r="414" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="B414">
         <v>0.97694999999999999</v>
@@ -10504,7 +10516,7 @@
         <v>0.61812500000000004</v>
       </c>
       <c r="F414" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
     </row>
   </sheetData>
